--- a/www/terminologies/ValueSet-JDV-J19-ModePriseEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J19-ModePriseEnCharge-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -306,7 +306,7 @@
     <t>58</t>
   </si>
   <si>
-    <t>Coordination de parcours</t>
+    <t>Suivi ou coordination de parcours</t>
   </si>
   <si>
     <t>59</t>

--- a/www/terminologies/ValueSet-JDV-J19-ModePriseEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J19-ModePriseEnCharge-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +313,12 @@
   </si>
   <si>
     <t>Equipe d'intervention mobile</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>Dispositif expérimental</t>
   </si>
   <si>
     <t/>
@@ -583,7 +589,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -891,15 +897,23 @@
         <v>100</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>102</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J19-ModePriseEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J19-ModePriseEnCharge-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="103">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,12 +313,6 @@
   </si>
   <si>
     <t>Equipe d'intervention mobile</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>Dispositif expérimental</t>
   </si>
   <si>
     <t/>
@@ -589,7 +583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -897,23 +891,15 @@
         <v>100</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>102</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
